--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107625</v>
+        <v>107633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107633</v>
+        <v>107726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107726</v>
+        <v>107750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107750</v>
+        <v>107763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107763</v>
+        <v>107772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107772</v>
+        <v>107777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>107777</v>
+        <v>107805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>108021</v>
+        <v>108024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>108111</v>
+        <v>108114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7433-2025 artfynd.xlsx
+++ b/artfynd/A 7433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128214431</v>
       </c>
       <c r="B2" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
